--- a/output/pdf_financials_xlsx/PWM.xlsx
+++ b/output/pdf_financials_xlsx/PWM.xlsx
@@ -4453,40 +4453,40 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>0.44913</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>0.864475</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>0.844544</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>0.749698</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>1.439287</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>2.295767</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>2.352124</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>3.014106</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>2.597561</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>2.265919</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>2.595734</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>2.086059</v>
       </c>
     </row>
     <row r="93">
@@ -5535,40 +5535,40 @@
         </is>
       </c>
       <c r="B118" s="3" t="n">
-        <v>0</v>
+        <v>-1.410008</v>
       </c>
       <c r="C118" s="3" t="n">
-        <v>0</v>
+        <v>-1.746666</v>
       </c>
       <c r="D118" s="3" t="n">
-        <v>1.275063</v>
+        <v>-0.115799</v>
       </c>
       <c r="E118" s="3" t="n">
-        <v>5.790099</v>
+        <v>5.702534</v>
       </c>
       <c r="F118" s="3" t="n">
-        <v>2.188652</v>
+        <v>1.461024</v>
       </c>
       <c r="G118" s="3" t="n">
-        <v>1.88</v>
+        <v>-0.132371</v>
       </c>
       <c r="H118" s="3" t="n">
-        <v>0</v>
+        <v>-0.188968</v>
       </c>
       <c r="I118" s="3" t="n">
-        <v>0</v>
+        <v>-0.154059</v>
       </c>
       <c r="J118" s="3" t="n">
-        <v>1.915226</v>
+        <v>0.767655</v>
       </c>
       <c r="K118" s="3" t="n">
-        <v>0.0052</v>
+        <v>-1.009504</v>
       </c>
       <c r="L118" s="3" t="n">
-        <v>0</v>
+        <v>-3.115529</v>
       </c>
       <c r="M118" s="3" t="n">
-        <v>0</v>
+        <v>-2.800771</v>
       </c>
     </row>
     <row r="119">
@@ -7312,7 +7312,11 @@
           <t>Reserves (Note 7)</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr">
         <is>
           <t>-</t>
@@ -8268,7 +8272,11 @@
           <t>Reserves (Note 8)</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr"/>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E29" s="5" t="n">
         <v>0.44913</v>
       </c>
@@ -11010,7 +11018,11 @@
           <t>Exploration and evaluation expenditures</t>
         </is>
       </c>
-      <c r="D67" t="inlineStr"/>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E67" s="5" t="n">
         <v>-1.410008</v>
       </c>

--- a/output/pdf_financials_xlsx/PWM.xlsx
+++ b/output/pdf_financials_xlsx/PWM.xlsx
@@ -879,10 +879,10 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.003941</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>5.2e-05</v>
       </c>
       <c r="D12" s="3" t="n">
         <v>0</v>
@@ -906,13 +906,13 @@
         <v>0</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0</v>
+        <v>0.126624</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0</v>
+        <v>0.126644</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>0</v>
+        <v>0.002809</v>
       </c>
     </row>
     <row r="13">
@@ -1584,10 +1584,10 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-1.459696</v>
+        <v>-1.463637</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-1.118417</v>
+        <v>-1.118469</v>
       </c>
       <c r="D27" s="3" t="n">
         <v>-1.690589</v>
@@ -1611,13 +1611,13 @@
         <v>-3.336263</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>-2.305608</v>
+        <v>-2.432232</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>-1.039898</v>
+        <v>-1.166542</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>-2.055231</v>
+        <v>-2.05804</v>
       </c>
     </row>
     <row r="28">
@@ -1670,10 +1670,10 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-1.455417</v>
+        <v>-1.459358</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-1.113388</v>
+        <v>-1.11344</v>
       </c>
       <c r="D29" s="3" t="n">
         <v>-1.684961</v>
@@ -1697,13 +1697,13 @@
         <v>-3.330361</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-2.305608</v>
+        <v>-2.432232</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>-1.039898</v>
+        <v>-1.166542</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>-2.055231</v>
+        <v>-2.05804</v>
       </c>
     </row>
     <row r="30">
@@ -1900,25 +1900,25 @@
         <v>0</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.005058</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.087863</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.007621</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.033668</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.743318</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.011598</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.013216</v>
       </c>
       <c r="J34" s="3" t="n">
         <v>0.626983</v>
@@ -1930,7 +1930,7 @@
         <v>2.14057</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>0.080565</v>
       </c>
     </row>
     <row r="35">
@@ -1986,25 +1986,25 @@
         <v>0</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.005058</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.087863</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.007621</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.033668</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0.45</v>
+        <v>1.193318</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.011598</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.013216</v>
       </c>
       <c r="J36" s="3" t="n">
         <v>0.626983</v>
@@ -2016,7 +2016,7 @@
         <v>2.14057</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>0.080565</v>
       </c>
     </row>
     <row r="37">
@@ -2502,25 +2502,25 @@
         <v>0.203239</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.023706</v>
+        <v>0.018648</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.093969</v>
+        <v>0.006106</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.007621</v>
+        <v>0</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.033668</v>
+        <v>0</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.785211</v>
+        <v>0.041893</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.039091</v>
+        <v>0.027493</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.014254</v>
+        <v>0.001038</v>
       </c>
       <c r="J48" s="3" t="n">
         <v>1.824194</v>
@@ -2532,7 +2532,7 @@
         <v>0.639888</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>0.283131</v>
+        <v>0.202566</v>
       </c>
     </row>
     <row r="49">
@@ -6446,7 +6446,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -18298,7 +18298,7 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E166" s="5" t="n">

--- a/output/pdf_financials_xlsx/PWM.xlsx
+++ b/output/pdf_financials_xlsx/PWM.xlsx
@@ -3340,40 +3340,40 @@
         </is>
       </c>
       <c r="B67" s="3" t="n">
-        <v>0</v>
+        <v>0.014</v>
       </c>
       <c r="C67" s="3" t="n">
-        <v>0</v>
+        <v>0.017</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="E67" s="3" t="n">
-        <v>0</v>
+        <v>0.016</v>
       </c>
       <c r="F67" s="3" t="n">
-        <v>0</v>
+        <v>0.042576</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>0</v>
+        <v>0.03876</v>
       </c>
       <c r="H67" s="3" t="n">
-        <v>0</v>
+        <v>0.052</v>
       </c>
       <c r="I67" s="3" t="n">
-        <v>0</v>
+        <v>0.598508</v>
       </c>
       <c r="J67" s="3" t="n">
-        <v>0</v>
+        <v>0.598508</v>
       </c>
       <c r="K67" s="3" t="n">
-        <v>0</v>
+        <v>0.633516</v>
       </c>
       <c r="L67" s="3" t="n">
-        <v>0</v>
+        <v>0.8742</v>
       </c>
       <c r="M67" s="3" t="n">
-        <v>0</v>
+        <v>0.848698</v>
       </c>
     </row>
     <row r="68">
@@ -4804,10 +4804,10 @@
         </is>
       </c>
       <c r="B101" s="3" t="n">
-        <v>0</v>
+        <v>0.006888</v>
       </c>
       <c r="C101" s="3" t="n">
-        <v>0</v>
+        <v>0.032881</v>
       </c>
       <c r="D101" s="3" t="n">
         <v>0</v>
@@ -5019,10 +5019,10 @@
         </is>
       </c>
       <c r="B106" s="3" t="n">
-        <v>-0.09941</v>
+        <v>-0.09252199999999999</v>
       </c>
       <c r="C106" s="3" t="n">
-        <v>0.128752</v>
+        <v>0.161633</v>
       </c>
       <c r="D106" s="3" t="n">
         <v>0.137207</v>
@@ -5421,10 +5421,10 @@
         <v>0</v>
       </c>
       <c r="G115" s="3" t="n">
-        <v>0</v>
+        <v>1.087665</v>
       </c>
       <c r="H115" s="3" t="n">
-        <v>0</v>
+        <v>0.198951</v>
       </c>
       <c r="I115" s="3" t="n">
         <v>0</v>
@@ -5439,7 +5439,7 @@
         <v>0</v>
       </c>
       <c r="M115" s="3" t="n">
-        <v>0</v>
+        <v>0.416411</v>
       </c>
     </row>
     <row r="116">
@@ -10870,7 +10870,11 @@
           <t>Proceeds from sale of investments</t>
         </is>
       </c>
-      <c r="D65" t="inlineStr"/>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E65" t="inlineStr">
         <is>
           <t>-</t>
@@ -11972,7 +11976,11 @@
           <t>Shares issued for cash</t>
         </is>
       </c>
-      <c r="D81" t="inlineStr"/>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E81" t="inlineStr">
         <is>
           <t>-</t>
@@ -13684,7 +13692,11 @@
           <t>Proceed from sale of marketable securities</t>
         </is>
       </c>
-      <c r="D104" t="inlineStr"/>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E104" t="inlineStr">
         <is>
           <t>-</t>
@@ -13758,7 +13770,11 @@
           <t>Proceeds from private placement</t>
         </is>
       </c>
-      <c r="D105" t="inlineStr"/>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E105" t="inlineStr">
         <is>
           <t>-</t>
@@ -14502,7 +14518,11 @@
           <t>Proceeds from sales of marketable securities</t>
         </is>
       </c>
-      <c r="D115" t="inlineStr"/>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E115" t="inlineStr">
         <is>
           <t>-</t>
@@ -14578,7 +14598,11 @@
           <t>Proceeds from share issuance</t>
         </is>
       </c>
-      <c r="D116" t="inlineStr"/>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E116" s="5" t="n">
         <v>1.92288</v>
       </c>
@@ -16778,7 +16802,11 @@
           <t>Decrease in GST receivable</t>
         </is>
       </c>
-      <c r="D145" t="inlineStr"/>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E145" s="5" t="n">
         <v>0.006888</v>
       </c>
